--- a/artfynd/A 13841-2022 artfynd.xlsx
+++ b/artfynd/A 13841-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 13841-2022 artfynd.xlsx
+++ b/artfynd/A 13841-2022 artfynd.xlsx
@@ -1729,7 +1729,7 @@
         <v>101512562</v>
       </c>
       <c r="B11" t="n">
-        <v>5113</v>
+        <v>5166</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>334130.6183008064</v>
+        <v>334131</v>
       </c>
       <c r="R11" t="n">
-        <v>6607592.448053617</v>
+        <v>6607592</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1808,19 +1808,9 @@
           <t>2022-05-09</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-05-09</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 13841-2022 artfynd.xlsx
+++ b/artfynd/A 13841-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1835,6 +1835,133 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>122892156</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Lilla Kroktjärnen, Lilla Kroktjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>334206</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6607643</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Karlanda</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Trummade flitigt</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Mikael Schulin</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Mikael Schulin</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 13841-2022 artfynd.xlsx
+++ b/artfynd/A 13841-2022 artfynd.xlsx
@@ -1840,7 +1840,7 @@
         <v>122892156</v>
       </c>
       <c r="B12" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 13841-2022 artfynd.xlsx
+++ b/artfynd/A 13841-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,42 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>101512368</v>
+        <v>101512407</v>
       </c>
       <c r="B2" t="n">
-        <v>73631</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6426</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>333628.6254326616</v>
+        <v>333756</v>
       </c>
       <c r="R2" t="n">
-        <v>6607605.55610727</v>
+        <v>6607524</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -751,19 +747,9 @@
           <t>2022-05-09</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-05-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>101512407</v>
+        <v>101512430</v>
       </c>
       <c r="B3" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -835,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>333755.6006520125</v>
+        <v>333806</v>
       </c>
       <c r="R3" t="n">
-        <v>6607523.830529192</v>
+        <v>6607449</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -868,28 +849,17 @@
           <t>2022-05-09</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-05-09</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -908,37 +878,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>101512410</v>
+        <v>101512460</v>
       </c>
       <c r="B4" t="n">
-        <v>94653</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2563</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Terpentinmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Geocalyx graveolens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schrad.) Nees</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -952,10 +917,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>333755.6006520125</v>
+        <v>333906</v>
       </c>
       <c r="R4" t="n">
-        <v>6607523.830529192</v>
+        <v>6607449</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -985,28 +950,17 @@
           <t>2022-05-09</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-05-09</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1025,37 +979,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>101512573</v>
+        <v>101512445</v>
       </c>
       <c r="B5" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6463</v>
+        <v>308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1068,10 +1017,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>334130.6183008064</v>
+        <v>333834</v>
       </c>
       <c r="R5" t="n">
-        <v>6607592.448053617</v>
+        <v>6607473</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1101,19 +1050,9 @@
           <t>2022-05-09</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-05-09</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1140,41 +1079,44 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>101512566</v>
+        <v>101512357</v>
       </c>
       <c r="B6" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80386</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>1152</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Grynlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pannaria conoplea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Ach.) Bory</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
@@ -1183,13 +1125,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>334130.6183008064</v>
+        <v>333669</v>
       </c>
       <c r="R6" t="n">
-        <v>6607592.448053617</v>
+        <v>6607693</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1216,27 +1158,18 @@
           <t>2022-05-09</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-05-09</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1255,37 +1188,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>101512460</v>
+        <v>101512432</v>
       </c>
       <c r="B7" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95944</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>2362</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blek stjärnmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Mnium stellare</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1299,10 +1227,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>333906.7555238548</v>
+        <v>333806</v>
       </c>
       <c r="R7" t="n">
-        <v>6607448.646592953</v>
+        <v>6607449</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1332,19 +1260,9 @@
           <t>2022-05-09</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-05-09</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,42 +1289,38 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>101512445</v>
+        <v>101512410</v>
       </c>
       <c r="B8" t="n">
-        <v>73686</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97594</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>308</v>
+        <v>2563</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Terpentinmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Geocalyx graveolens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Schrad.) Nees</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1414,10 +1328,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>333834.1331071719</v>
+        <v>333756</v>
       </c>
       <c r="R8" t="n">
-        <v>6607472.663432037</v>
+        <v>6607524</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1447,27 +1361,18 @@
           <t>2022-05-09</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-05-09</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1486,15 +1391,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>101512372</v>
+        <v>101512566</v>
       </c>
       <c r="B9" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1502,21 +1402,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229497</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1529,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>333628.6254326616</v>
+        <v>334131</v>
       </c>
       <c r="R9" t="n">
-        <v>6607605.55610727</v>
+        <v>6607592</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1562,28 +1462,17 @@
           <t>2022-05-09</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-05-09</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1602,64 +1491,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>101512357</v>
+        <v>1829763</v>
       </c>
       <c r="B10" t="n">
-        <v>78521</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1152</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grynlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pannaria conoplea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bory</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Söder Stora Kroktjärnen, Vrm</t>
+          <t>NORR ORMETJÄRN (11B2h11), Vrm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>333668.5645896816</v>
+        <v>333939</v>
       </c>
       <c r="R10" t="n">
-        <v>6607692.558771814</v>
+        <v>6607574</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1683,22 +1556,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-05-09</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1996-02-01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-05-09</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1996-02-01</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>110127111 / ALE SARM / Tämligen allmän (2)  / OBJ.AREA:26,4 ha</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1707,67 +1575,59 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Jan Rees</t>
+          <t>Niklas Lönnell</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Jan Rees, Jeanette Fahlstad</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens naturvärdesobjekt</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>101512562</v>
+        <v>101512398</v>
       </c>
       <c r="B11" t="n">
-        <v>5166</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1775,10 +1635,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>334131</v>
+        <v>333679</v>
       </c>
       <c r="R11" t="n">
-        <v>6607592</v>
+        <v>6607532</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1819,6 +1679,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1837,15 +1698,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122892156</v>
+        <v>101512368</v>
       </c>
       <c r="B12" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1853,47 +1709,40 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6426</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lilla Kroktjärnen, Lilla Kroktjärnen, Vrm</t>
+          <t>Söder Stora Kroktjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>334206</v>
+        <v>333629</v>
       </c>
       <c r="R12" t="n">
-        <v>6607643</v>
+        <v>6607605</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1917,27 +1766,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>16:21</t>
+          <t>2022-05-09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>16:21</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Trummade flitigt</t>
+          <t>2022-05-09</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1946,21 +1780,451 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
+          <t>Jan Rees</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Jan Rees, Jeanette Fahlstad</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>101512573</v>
+      </c>
+      <c r="B13" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Söder Stora Kroktjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>334131</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6607592</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Karlanda</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2022-05-09</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2022-05-09</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Jan Rees</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Jan Rees, Jeanette Fahlstad</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>122892156</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Lilla Kroktjärnen, Lilla Kroktjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>334206</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6607643</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Karlanda</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Trummade flitigt</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
           <t>Mikael Schulin</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
+      <c r="AX14" t="inlineStr">
         <is>
           <t>Mikael Schulin</t>
         </is>
       </c>
-      <c r="AY12" t="inlineStr"/>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>101512562</v>
+      </c>
+      <c r="B15" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Söder Stora Kroktjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>334131</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6607592</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Karlanda</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2022-05-09</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2022-05-09</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Jan Rees</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Jan Rees, Jeanette Fahlstad</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>101512372</v>
+      </c>
+      <c r="B16" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Söder Stora Kroktjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>333629</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6607605</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Karlanda</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2022-05-09</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2022-05-09</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Jan Rees</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Jan Rees, Jeanette Fahlstad</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
